--- a/directorio.xlsx
+++ b/directorio.xlsx
@@ -3903,8 +3903,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C89D2D723E31AD49A99754977A535CD5" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="fc6e06cd991f76fd4713db0f638620e9">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="90a45df5-754a-416f-a615-16c5d1ea499f" xmlns:ns3="6a760d76-56c9-4564-aaf3-217c3e3877a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1161a42123d2e798d184a36c41e3225a" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C89D2D723E31AD49A99754977A535CD5" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="001b7acd8f2976038f93c737239349ab">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="90a45df5-754a-416f-a615-16c5d1ea499f" xmlns:ns3="6a760d76-56c9-4564-aaf3-217c3e3877a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5799675022c05d4610dc618118321a1c" ns2:_="" ns3:_="">
     <xsd:import namespace="90a45df5-754a-416f-a615-16c5d1ea499f"/>
     <xsd:import namespace="6a760d76-56c9-4564-aaf3-217c3e3877a9"/>
     <xsd:element name="properties">
@@ -3924,6 +3924,8 @@
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:Descripcion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3988,6 +3990,16 @@
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -4127,22 +4139,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B63BDED-B0A5-4237-A333-379FF9EE0A53}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="90a45df5-754a-416f-a615-16c5d1ea499f"/>
-    <ds:schemaRef ds:uri="6a760d76-56c9-4564-aaf3-217c3e3877a9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{892654F3-2683-4BDB-8C91-E516E40272F3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
